--- a/healthcare_forms/015_dental_referral_form--healthcare_forms.xlsx
+++ b/healthcare_forms/015_dental_referral_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'medicare',_'text':_'medicare'}</t>
+          <t>medicare</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Medicare', 'text': 'Medicare'}</t>
+          <t>Medicare</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medicaid',_'text':_'medicaid'}</t>
+          <t>medicaid</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medicaid', 'text': 'Medicaid'}</t>
+          <t>Medicaid</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'private',_'text':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Private', 'text': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'text':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other', 'text': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'uninsured',_'text':_'uninsured'}</t>
+          <t>uninsured</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Uninsured', 'text': 'Uninsured'}</t>
+          <t>Uninsured</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'emergency',_'text':_'emergency'}</t>
+          <t>emergency</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Emergency', 'text': 'Emergency'}</t>
+          <t>Emergency</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'routine',_'text':_'routine'}</t>
+          <t>routine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Routine', 'text': 'Routine'}</t>
+          <t>Routine</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'cosmetic',_'text':_'cosmetic'}</t>
+          <t>cosmetic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Cosmetic', 'text': 'Cosmetic'}</t>
+          <t>Cosmetic</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'text':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other', 'text': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'referral',_'text':_'referral'}</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Referral', 'text': 'Referral'}</t>
+          <t>Referral</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'dentist',_'text':_'dentist'}</t>
+          <t>dentist</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Dentist', 'text': 'Dentist'}</t>
+          <t>Dentist</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'doctor',_'text':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Doctor', 'text': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'specialist',_'text':_'specialist'}</t>
+          <t>specialist</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Specialist', 'text': 'Specialist'}</t>
+          <t>Specialist</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'text':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other', 'text': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
